--- a/bills/JXZFSP/-5230462985/fc69bc8101c55c7eeca718e92227fbe9b026ec9ec3afcc79a6c130783937e004/bill-all.xlsx
+++ b/bills/JXZFSP/-5230462985/fc69bc8101c55c7eeca718e92227fbe9b026ec9ec3afcc79a6c130783937e004/bill-all.xlsx
@@ -72,144 +72,186 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>07/13 23:35:59</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>26000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1925.93</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>lao1_vip</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1925.93</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1925.93</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5230462985/fc69bc8101c55c7eeca718e92227fbe9b026ec9ec3afcc79a6c130783937e004/bill-all.xlsx
+++ b/bills/JXZFSP/-5230462985/fc69bc8101c55c7eeca718e92227fbe9b026ec9ec3afcc79a6c130783937e004/bill-all.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/13 23:36:17</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>23800</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1762.96</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>lao1_vip</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>07/13 23:35:59</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>26000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>13.5</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>1925.93</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>lao1_vip</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>26000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1925.93</t>
+          <t>49800</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3688.89</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1925.93</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>3688.89</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5230462985/fc69bc8101c55c7eeca718e92227fbe9b026ec9ec3afcc79a6c130783937e004/bill-all.xlsx
+++ b/bills/JXZFSP/-5230462985/fc69bc8101c55c7eeca718e92227fbe9b026ec9ec3afcc79a6c130783937e004/bill-all.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>07/14 00:17:33</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>3688</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>lao1_vip</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>49800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3688.89</t>
+          <t>49800</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3688.89</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>3688</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>3688.89</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.89</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5230462985/fc69bc8101c55c7eeca718e92227fbe9b026ec9ec3afcc79a6c130783937e004/bill-all.xlsx
+++ b/bills/JXZFSP/-5230462985/fc69bc8101c55c7eeca718e92227fbe9b026ec9ec3afcc79a6c130783937e004/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/13 23:36:17</t>
+          <t>07/14 21:09:56</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23800</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1762.96</t>
+          <t>370.37</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,210 +117,252 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>07/13 23:36:17</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>23800</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1762.96</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>lao1_vip</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>07/13 23:35:59</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>26000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>13.5</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>1925.93</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>lao1_vip</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>07/14 00:17:33</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>3688</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>lao1_vip</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>49800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3688.89</t>
+          <t>54800</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3688</t>
+          <t>4059.26</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>3688</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.89</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>371.26</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5230462985/fc69bc8101c55c7eeca718e92227fbe9b026ec9ec3afcc79a6c130783937e004/bill-all.xlsx
+++ b/bills/JXZFSP/-5230462985/fc69bc8101c55c7eeca718e92227fbe9b026ec9ec3afcc79a6c130783937e004/bill-all.xlsx
@@ -286,83 +286,110 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>07/14 22:31:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>lao1_vip</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>07/14 00:17:33</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>3688</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>lao1_vip</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>lao1_vip</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>54800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4059.26</t>
+          <t>54800</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3688</t>
+          <t>4059.26</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>4058</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>371.26</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1.26</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5230462985/fc69bc8101c55c7eeca718e92227fbe9b026ec9ec3afcc79a6c130783937e004/bill-all.xlsx
+++ b/bills/JXZFSP/-5230462985/fc69bc8101c55c7eeca718e92227fbe9b026ec9ec3afcc79a6c130783937e004/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/14 21:09:56</t>
+          <t>07/15 01:02:13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>48000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>370.37</t>
+          <t>3478.26</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>lao1_vip</t>
+          <t>af_vip01</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/13 23:36:17</t>
+          <t>07/14 21:09:56</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>23800</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1762.96</t>
+          <t>370.37</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,237 +159,279 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>07/13 23:36:17</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>23800</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1762.96</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>lao1_vip</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>07/13 23:35:59</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>26000</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>13.5</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>1925.93</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>lao1_vip</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/14 22:31:00</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>lao1_vip</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>07/14 22:31:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>lao1_vip</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>07/14 00:17:33</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>3688</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>lao1_vip</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>54800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4059.26</t>
+          <t>102800</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>7537.52</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>4058</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1.26</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>3479.52</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5230462985/fc69bc8101c55c7eeca718e92227fbe9b026ec9ec3afcc79a6c130783937e004/bill-all.xlsx
+++ b/bills/JXZFSP/-5230462985/fc69bc8101c55c7eeca718e92227fbe9b026ec9ec3afcc79a6c130783937e004/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/15 01:02:13</t>
+          <t>07/15 18:54:42</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>48000</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3478.26</t>
+          <t>2536.23</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>af_vip01</t>
+          <t>lao1_vip</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/14 21:09:56</t>
+          <t>07/15 01:02:13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>48000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>370.37</t>
+          <t>3478.26</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>lao1_vip</t>
+          <t>af_vip01</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/13 23:36:17</t>
+          <t>07/14 21:09:56</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>23800</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1762.96</t>
+          <t>370.37</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,237 +201,279 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>07/13 23:36:17</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>23800</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1762.96</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>lao1_vip</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>07/13 23:35:59</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>26000</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>13.5</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>1925.93</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>lao1_vip</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>lao1_vip</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/14 22:31:00</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>lao1_vip</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>07/14 22:31:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>lao1_vip</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>07/14 00:17:33</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>3688</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>lao1_vip</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>lao1_vip</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>102800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7537.52</t>
+          <t>137800</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>10073.75</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>4058</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3479.52</t>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>6015.75</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5230462985/fc69bc8101c55c7eeca718e92227fbe9b026ec9ec3afcc79a6c130783937e004/bill-all.xlsx
+++ b/bills/JXZFSP/-5230462985/fc69bc8101c55c7eeca718e92227fbe9b026ec9ec3afcc79a6c130783937e004/bill-all.xlsx
@@ -370,12 +370,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/14 22:31:00</t>
+          <t>07/15 19:00:42</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>2536</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -397,83 +397,110 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>07/14 22:31:00</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>lao1_vip</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>07/14 00:17:33</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>3688</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>lao1_vip</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>lao1_vip</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>137800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10073.75</t>
+          <t>137800</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>10073.75</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>6594</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>6015.75</t>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>3479.75</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5230462985/fc69bc8101c55c7eeca718e92227fbe9b026ec9ec3afcc79a6c130783937e004/bill-all.xlsx
+++ b/bills/JXZFSP/-5230462985/fc69bc8101c55c7eeca718e92227fbe9b026ec9ec3afcc79a6c130783937e004/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/15 18:54:42</t>
+          <t>07/16 00:26:23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>42000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2536.23</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/15 01:02:13</t>
+          <t>07/15 18:54:42</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>48000</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3478.26</t>
+          <t>2536.23</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>af_vip01</t>
+          <t>lao1_vip</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/14 21:09:56</t>
+          <t>07/15 01:02:13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>48000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>370.37</t>
+          <t>3478.26</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>lao1_vip</t>
+          <t>af_vip01</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/13 23:36:17</t>
+          <t>07/14 21:09:56</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>23800</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1762.96</t>
+          <t>370.37</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,166 +243,181 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>07/13 23:36:17</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>23800</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1762.96</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>lao1_vip</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>07/13 23:35:59</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>26000</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>13.5</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>1925.93</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>lao1_vip</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>lao1_vip</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/15 19:00:42</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2536</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>lao1_vip</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/14 22:31:00</t>
+          <t>07/15 19:00:42</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>2536</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -424,83 +439,110 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>07/14 22:31:00</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>lao1_vip</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>07/14 00:17:33</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>3688</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>lao1_vip</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>lao1_vip</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>137800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10073.75</t>
+          <t>179800</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>6594</t>
+          <t>13073.75</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>6594</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3479.75</t>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>6479.75</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5230462985/fc69bc8101c55c7eeca718e92227fbe9b026ec9ec3afcc79a6c130783937e004/bill-all.xlsx
+++ b/bills/JXZFSP/-5230462985/fc69bc8101c55c7eeca718e92227fbe9b026ec9ec3afcc79a6c130783937e004/bill-all.xlsx
@@ -412,12 +412,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/15 19:00:42</t>
+          <t>07/16 00:41:02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2536</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -439,12 +439,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/14 22:31:00</t>
+          <t>07/15 19:00:42</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>2536</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -466,83 +466,110 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>07/14 22:31:00</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>lao1_vip</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>07/14 00:17:33</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>3688</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>lao1_vip</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>lao1_vip</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>179800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13073.75</t>
+          <t>179800</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>6594</t>
+          <t>13073.75</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>9594</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>6479.75</t>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>3479.75</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5230462985/fc69bc8101c55c7eeca718e92227fbe9b026ec9ec3afcc79a6c130783937e004/bill-all.xlsx
+++ b/bills/JXZFSP/-5230462985/fc69bc8101c55c7eeca718e92227fbe9b026ec9ec3afcc79a6c130783937e004/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/16 00:26:23</t>
+          <t>07/16 01:15:43</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>42000</t>
+          <t>25000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1785.71</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/15 18:54:42</t>
+          <t>07/16 00:26:23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>42000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2536.23</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/15 01:02:13</t>
+          <t>07/15 18:54:42</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48000</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3478.26</t>
+          <t>2536.23</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>af_vip01</t>
+          <t>lao1_vip</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/14 21:09:56</t>
+          <t>07/15 01:02:13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>48000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>370.37</t>
+          <t>3478.26</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>lao1_vip</t>
+          <t>af_vip01</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/13 23:36:17</t>
+          <t>07/14 21:09:56</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>23800</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1762.96</t>
+          <t>370.37</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,166 +285,181 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>07/13 23:36:17</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>23800</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1762.96</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>lao1_vip</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>07/13 23:35:59</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>26000</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>13.5</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>1925.93</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>lao1_vip</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>lao1_vip</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/16 00:41:02</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>lao1_vip</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/15 19:00:42</t>
+          <t>07/16 00:41:02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2536</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -466,12 +481,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/14 22:31:00</t>
+          <t>07/15 19:00:42</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>2536</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -493,83 +508,110 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>07/14 22:31:00</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>lao1_vip</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>07/14 00:17:33</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>3688</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>lao1_vip</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>lao1_vip</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>179800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13073.75</t>
+          <t>204800</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>14859.47</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>9594</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3479.75</t>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>5265.47</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5230462985/fc69bc8101c55c7eeca718e92227fbe9b026ec9ec3afcc79a6c130783937e004/bill-all.xlsx
+++ b/bills/JXZFSP/-5230462985/fc69bc8101c55c7eeca718e92227fbe9b026ec9ec3afcc79a6c130783937e004/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/16 01:15:43</t>
+          <t>07/16 01:43:13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25000</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1785.71</t>
+          <t>2142.86</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/16 00:26:23</t>
+          <t>07/16 01:15:43</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>42000</t>
+          <t>25000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1785.71</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/15 18:54:42</t>
+          <t>07/16 00:26:23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>42000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2536.23</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/15 01:02:13</t>
+          <t>07/15 18:54:42</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>48000</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3478.26</t>
+          <t>2536.23</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>af_vip01</t>
+          <t>lao1_vip</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/14 21:09:56</t>
+          <t>07/15 01:02:13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>48000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>370.37</t>
+          <t>3478.26</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>lao1_vip</t>
+          <t>af_vip01</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/13 23:36:17</t>
+          <t>07/14 21:09:56</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>23800</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1762.96</t>
+          <t>370.37</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,166 +327,181 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>07/13 23:36:17</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>23800</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1762.96</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>lao1_vip</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>07/13 23:35:59</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>26000</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>13.5</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>1925.93</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>lao1_vip</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>lao1_vip</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/16 00:41:02</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>lao1_vip</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/15 19:00:42</t>
+          <t>07/16 00:41:02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2536</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -508,12 +523,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/14 22:31:00</t>
+          <t>07/15 19:00:42</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>2536</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -535,83 +550,110 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>07/14 22:31:00</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>lao1_vip</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>07/14 00:17:33</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>3688</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>lao1_vip</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>lao1_vip</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>204800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14859.47</t>
+          <t>234800</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>17002.32</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>9594</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>5265.47</t>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>7408.32</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5230462985/fc69bc8101c55c7eeca718e92227fbe9b026ec9ec3afcc79a6c130783937e004/bill-all.xlsx
+++ b/bills/JXZFSP/-5230462985/fc69bc8101c55c7eeca718e92227fbe9b026ec9ec3afcc79a6c130783937e004/bill-all.xlsx
@@ -496,12 +496,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/16 00:41:02</t>
+          <t>07/16 04:19:55</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -523,12 +523,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/15 19:00:42</t>
+          <t>07/16 00:41:02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2536</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -550,12 +550,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/14 22:31:00</t>
+          <t>07/15 19:00:42</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>2536</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -577,83 +577,110 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>07/14 22:31:00</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>lao1_vip</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>07/14 00:17:33</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>3688</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>lao1_vip</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>lao1_vip</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>234800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>17002.32</t>
+          <t>234800</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>17002.32</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>13094</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>7408.32</t>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>3908.32</t>
         </is>
       </c>
     </row>
